--- a/Project Outputs for uz_per_torque_box/Rev01/BOM/BOM_JLC-uz_per_torque_box(Default)_JLC_Upload.xlsx
+++ b/Project Outputs for uz_per_torque_box/Rev01/BOM/BOM_JLC-uz_per_torque_box(Default)_JLC_Upload.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GIT\UltraZohm\pcb_design\uz_per_torque_box\Project Outputs for uz_per_torque_box\Rev01\BOM\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AEDFB074-1C7B-45B3-83A6-0A224B947417}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{F770107E-0974-4AE9-B8E3-C0A649133B67}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="67080" yWindow="-2460" windowWidth="38640" windowHeight="21120" xr2:uid="{D254624D-B5F4-452F-BAD6-1683F1703D90}"/>
+    <workbookView xWindow="28680" yWindow="-2340" windowWidth="38640" windowHeight="21120" xr2:uid="{FC3DBFCE-7EE3-42A4-A146-41CE7DA3C43B}"/>
   </bookViews>
   <sheets>
     <sheet name="BOM_JLC-uz_per_torque_box(Defau" sheetId="1" r:id="rId1"/>
@@ -752,7 +752,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5CD086BD-609A-4EE1-B125-230C06DAAB6D}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5F6B8435-3D0D-449F-AEE6-4A5FF8FCFF14}">
   <dimension ref="A1:K17"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
